--- a/outputs/52964.xlsx
+++ b/outputs/52964.xlsx
@@ -2395,8 +2395,8 @@
         <v>27597</v>
       </c>
       <c r="C2" s="18" t="n">
-        <f aca="false">INDEX($U$2:$U$124,MATCH($A2,$Q$2:$Q$124,0))-INDEX($Y$2:$Y$124,MATCH($A2,$Q$2:$Q$124,0))</f>
-        <v>-17</v>
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A2,$Q$2:$Q$124,0))-$U2,0)</f>
+        <v>17</v>
       </c>
       <c r="D2" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF2,"*delirium*"),"Postoperative Delirium","No")</f>
@@ -2547,6 +2547,10 @@
       <c r="A3" s="1" t="n">
         <v>73866</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A3,$Q$2:$Q$124,0))-$U3,0)</f>
+        <v>-44287</v>
+      </c>
       <c r="D3" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF3,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -2687,6 +2691,10 @@
       <c r="A4" s="1" t="n">
         <v>83848</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A4,$Q$2:$Q$124,0))-$U4,0)</f>
+        <v>-44371</v>
+      </c>
       <c r="D4" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF4,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -2830,6 +2838,10 @@
       <c r="A5" s="1" t="n">
         <v>95560</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A5,$Q$2:$Q$124,0))-$U5,0)</f>
+        <v>-44323</v>
+      </c>
       <c r="D5" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF5,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -2973,6 +2985,10 @@
       <c r="A6" s="1" t="n">
         <v>113639</v>
       </c>
+      <c r="C6" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A6,$Q$2:$Q$124,0))-$U6,0)</f>
+        <v>-44328</v>
+      </c>
       <c r="D6" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF6,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3119,6 +3135,10 @@
       <c r="A7" s="1" t="n">
         <v>152785</v>
       </c>
+      <c r="C7" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A7,$Q$2:$Q$124,0))-$U7,0)</f>
+        <v>-44368</v>
+      </c>
       <c r="D7" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF7,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3265,6 +3285,10 @@
       <c r="A8" s="1" t="n">
         <v>205716</v>
       </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A8,$Q$2:$Q$124,0))-$U8,0)</f>
+        <v>-44293</v>
+      </c>
       <c r="D8" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF8,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3408,6 +3432,10 @@
       <c r="A9" s="1" t="n">
         <v>226886</v>
       </c>
+      <c r="C9" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A9,$Q$2:$Q$124,0))-$U9,0)</f>
+        <v>-44377</v>
+      </c>
       <c r="D9" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF9,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3551,6 +3579,10 @@
       <c r="A10" s="1" t="n">
         <v>245827</v>
       </c>
+      <c r="C10" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A10,$Q$2:$Q$124,0))-$U10,0)</f>
+        <v>-44376</v>
+      </c>
       <c r="D10" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF10,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3697,6 +3729,10 @@
       <c r="A11" s="1" t="n">
         <v>256792</v>
       </c>
+      <c r="C11" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A11,$Q$2:$Q$124,0))-$U11,0)</f>
+        <v>-44369</v>
+      </c>
       <c r="D11" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF11,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3846,6 +3882,10 @@
       <c r="A12" s="1" t="n">
         <v>260828</v>
       </c>
+      <c r="C12" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A12,$Q$2:$Q$124,0))-$U12,0)</f>
+        <v>-44299</v>
+      </c>
       <c r="D12" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF12,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -3995,6 +4035,10 @@
       <c r="A13" s="1" t="n">
         <v>263392</v>
       </c>
+      <c r="C13" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A13,$Q$2:$Q$124,0))-$U13,0)</f>
+        <v>-44299</v>
+      </c>
       <c r="D13" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF13,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -4141,6 +4185,10 @@
       <c r="A14" s="1" t="n">
         <v>292144</v>
       </c>
+      <c r="C14" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A14,$Q$2:$Q$124,0))-$U14,0)</f>
+        <v>-44335</v>
+      </c>
       <c r="D14" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF14,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -4290,6 +4338,10 @@
       <c r="A15" s="1" t="n">
         <v>355321</v>
       </c>
+      <c r="C15" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A15,$Q$2:$Q$124,0))-$U15,0)</f>
+        <v>-44363</v>
+      </c>
       <c r="D15" s="19" t="str">
         <f aca="false">IF(COUNTIF(AF15,"*delirium*"),"Postoperative Delirium","No")</f>
         <v>No</v>
@@ -4434,6 +4486,10 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28"/>
+      <c r="C16" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A16,$Q$2:$Q$124,0))-$U16,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q16" s="1" t="n">
         <v>320838</v>
       </c>
@@ -4542,6 +4598,10 @@
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29"/>
+      <c r="C17" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A17,$Q$2:$Q$124,0))-$U17,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q17" s="1" t="n">
         <v>328987</v>
       </c>
@@ -4650,6 +4710,10 @@
     </row>
     <row r="18" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28"/>
+      <c r="C18" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A18,$Q$2:$Q$124,0))-$U18,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q18" s="1" t="n">
         <v>355321</v>
       </c>
@@ -4758,6 +4822,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29"/>
+      <c r="C19" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A19,$Q$2:$Q$124,0))-$U19,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q19" s="1" t="n">
         <v>359893</v>
       </c>
@@ -4863,6 +4931,10 @@
     </row>
     <row r="20" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28"/>
+      <c r="C20" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A20,$Q$2:$Q$124,0))-$U20,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q20" s="1" t="n">
         <v>366526</v>
       </c>
@@ -4971,6 +5043,10 @@
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29"/>
+      <c r="C21" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A21,$Q$2:$Q$124,0))-$U21,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q21" s="1" t="n">
         <v>397067</v>
       </c>
@@ -5079,6 +5155,10 @@
     </row>
     <row r="22" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28"/>
+      <c r="C22" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A22,$Q$2:$Q$124,0))-$U22,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q22" s="1" t="n">
         <v>409300</v>
       </c>
@@ -5184,6 +5264,10 @@
     </row>
     <row r="23" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29"/>
+      <c r="C23" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A23,$Q$2:$Q$124,0))-$U23,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q23" s="1" t="n">
         <v>423432</v>
       </c>
@@ -5295,6 +5379,10 @@
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
+      <c r="C24" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A24,$Q$2:$Q$124,0))-$U24,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q24" s="1" t="n">
         <v>430793</v>
       </c>
@@ -5403,6 +5491,10 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="29"/>
+      <c r="C25" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A25,$Q$2:$Q$124,0))-$U25,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q25" s="1" t="n">
         <v>473981</v>
       </c>
@@ -5514,6 +5606,10 @@
     </row>
     <row r="26" customFormat="false" ht="323.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28"/>
+      <c r="C26" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A26,$Q$2:$Q$124,0))-$U26,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q26" s="1" t="n">
         <v>482404</v>
       </c>
@@ -5622,6 +5718,10 @@
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
+      <c r="C27" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A27,$Q$2:$Q$124,0))-$U27,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q27" s="1" t="n">
         <v>485672</v>
       </c>
@@ -5724,6 +5824,10 @@
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28"/>
+      <c r="C28" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A28,$Q$2:$Q$124,0))-$U28,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q28" s="1" t="n">
         <v>517399</v>
       </c>
@@ -5835,6 +5939,10 @@
     </row>
     <row r="29" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29"/>
+      <c r="C29" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A29,$Q$2:$Q$124,0))-$U29,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q29" s="1" t="n">
         <v>524710</v>
       </c>
@@ -5946,6 +6054,10 @@
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28"/>
+      <c r="C30" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A30,$Q$2:$Q$124,0))-$U30,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q30" s="1" t="n">
         <v>526889</v>
       </c>
@@ -6051,6 +6163,10 @@
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29"/>
+      <c r="C31" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A31,$Q$2:$Q$124,0))-$U31,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q31" s="1" t="n">
         <v>548750</v>
       </c>
@@ -6156,6 +6272,10 @@
     </row>
     <row r="32" customFormat="false" ht="350.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28"/>
+      <c r="C32" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A32,$Q$2:$Q$124,0))-$U32,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q32" s="1" t="n">
         <v>548867</v>
       </c>
@@ -6264,6 +6384,10 @@
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
+      <c r="C33" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A33,$Q$2:$Q$124,0))-$U33,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q33" s="1" t="n">
         <v>553974</v>
       </c>
@@ -6375,6 +6499,10 @@
     </row>
     <row r="34" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28"/>
+      <c r="C34" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A34,$Q$2:$Q$124,0))-$U34,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q34" s="1" t="n">
         <v>572909</v>
       </c>
@@ -6486,6 +6614,10 @@
     </row>
     <row r="35" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29"/>
+      <c r="C35" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A35,$Q$2:$Q$124,0))-$U35,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q35" s="1" t="n">
         <v>580092</v>
       </c>
@@ -6591,6 +6723,10 @@
     </row>
     <row r="36" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28"/>
+      <c r="C36" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A36,$Q$2:$Q$124,0))-$U36,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q36" s="1" t="n">
         <v>580092</v>
       </c>
@@ -6696,6 +6832,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29"/>
+      <c r="C37" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A37,$Q$2:$Q$124,0))-$U37,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q37" s="1" t="n">
         <v>622225</v>
       </c>
@@ -6804,6 +6944,10 @@
     </row>
     <row r="38" customFormat="false" ht="793.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28"/>
+      <c r="C38" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A38,$Q$2:$Q$124,0))-$U38,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q38" s="1" t="n">
         <v>646271</v>
       </c>
@@ -6915,6 +7059,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29"/>
+      <c r="C39" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A39,$Q$2:$Q$124,0))-$U39,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q39" s="1" t="n">
         <v>659086</v>
       </c>
@@ -7020,6 +7168,10 @@
     </row>
     <row r="40" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28"/>
+      <c r="C40" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A40,$Q$2:$Q$124,0))-$U40,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q40" s="1" t="n">
         <v>673614</v>
       </c>
@@ -7131,6 +7283,10 @@
     </row>
     <row r="41" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29"/>
+      <c r="C41" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A41,$Q$2:$Q$124,0))-$U41,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q41" s="1" t="n">
         <v>718163</v>
       </c>
@@ -7239,6 +7395,10 @@
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28"/>
+      <c r="C42" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A42,$Q$2:$Q$124,0))-$U42,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q42" s="1" t="n">
         <v>729418</v>
       </c>
@@ -7344,6 +7504,10 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="29"/>
+      <c r="C43" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A43,$Q$2:$Q$124,0))-$U43,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q43" s="1" t="n">
         <v>733212</v>
       </c>
@@ -7449,6 +7613,10 @@
     </row>
     <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28"/>
+      <c r="C44" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A44,$Q$2:$Q$124,0))-$U44,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q44" s="1" t="n">
         <v>803377</v>
       </c>
@@ -7557,6 +7725,10 @@
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="29"/>
+      <c r="C45" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A45,$Q$2:$Q$124,0))-$U45,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q45" s="1" t="n">
         <v>815967</v>
       </c>
@@ -7662,6 +7834,10 @@
     </row>
     <row r="46" customFormat="false" ht="229.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28"/>
+      <c r="C46" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A46,$Q$2:$Q$124,0))-$U46,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q46" s="1" t="n">
         <v>827097</v>
       </c>
@@ -7767,6 +7943,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29"/>
+      <c r="C47" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A47,$Q$2:$Q$124,0))-$U47,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q47" s="1" t="n">
         <v>841825</v>
       </c>
@@ -7869,6 +8049,10 @@
     </row>
     <row r="48" customFormat="false" ht="712.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28"/>
+      <c r="C48" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A48,$Q$2:$Q$124,0))-$U48,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q48" s="1" t="n">
         <v>857441</v>
       </c>
@@ -7980,6 +8164,10 @@
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="29"/>
+      <c r="C49" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A49,$Q$2:$Q$124,0))-$U49,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q49" s="1" t="n">
         <v>867507</v>
       </c>
@@ -8085,6 +8273,10 @@
     </row>
     <row r="50" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28"/>
+      <c r="C50" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A50,$Q$2:$Q$124,0))-$U50,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q50" s="1" t="n">
         <v>873065</v>
       </c>
@@ -8190,6 +8382,10 @@
     </row>
     <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="29"/>
+      <c r="C51" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A51,$Q$2:$Q$124,0))-$U51,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q51" s="1" t="n">
         <v>903896</v>
       </c>
@@ -8295,6 +8491,10 @@
     </row>
     <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="28"/>
+      <c r="C52" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A52,$Q$2:$Q$124,0))-$U52,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q52" s="1" t="n">
         <v>981670</v>
       </c>
@@ -8403,6 +8603,10 @@
     </row>
     <row r="53" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="29"/>
+      <c r="C53" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A53,$Q$2:$Q$124,0))-$U53,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q53" s="1" t="n">
         <v>1026665</v>
       </c>
@@ -8511,6 +8715,10 @@
     </row>
     <row r="54" customFormat="false" ht="565.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28"/>
+      <c r="C54" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A54,$Q$2:$Q$124,0))-$U54,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q54" s="1" t="n">
         <v>1030186</v>
       </c>
@@ -8625,6 +8833,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="29"/>
+      <c r="C55" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A55,$Q$2:$Q$124,0))-$U55,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q55" s="1" t="n">
         <v>1046042</v>
       </c>
@@ -8733,6 +8945,10 @@
     </row>
     <row r="56" customFormat="false" ht="766.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="28"/>
+      <c r="C56" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A56,$Q$2:$Q$124,0))-$U56,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q56" s="1" t="n">
         <v>1056629</v>
       </c>
@@ -8844,6 +9060,10 @@
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="29"/>
+      <c r="C57" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A57,$Q$2:$Q$124,0))-$U57,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q57" s="1" t="n">
         <v>1137650</v>
       </c>
@@ -8955,6 +9175,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28"/>
+      <c r="C58" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A58,$Q$2:$Q$124,0))-$U58,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q58" s="1" t="n">
         <v>1168614</v>
       </c>
@@ -9060,6 +9284,10 @@
     </row>
     <row r="59" customFormat="false" ht="498.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="29"/>
+      <c r="C59" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A59,$Q$2:$Q$124,0))-$U59,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q59" s="1" t="n">
         <v>1170943</v>
       </c>
@@ -9171,6 +9399,10 @@
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="28"/>
+      <c r="C60" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A60,$Q$2:$Q$124,0))-$U60,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q60" s="1" t="n">
         <v>1172485</v>
       </c>
@@ -9279,6 +9511,10 @@
     </row>
     <row r="61" customFormat="false" ht="726.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="29"/>
+      <c r="C61" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A61,$Q$2:$Q$124,0))-$U61,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q61" s="1" t="n">
         <v>1194115</v>
       </c>
@@ -9390,6 +9626,10 @@
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28"/>
+      <c r="C62" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A62,$Q$2:$Q$124,0))-$U62,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q62" s="1" t="n">
         <v>1258979</v>
       </c>
@@ -9495,6 +9735,10 @@
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="29"/>
+      <c r="C63" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A63,$Q$2:$Q$124,0))-$U63,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q63" s="1" t="n">
         <v>1281492</v>
       </c>
@@ -9600,6 +9844,10 @@
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="28"/>
+      <c r="C64" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A64,$Q$2:$Q$124,0))-$U64,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q64" s="1" t="n">
         <v>1306891</v>
       </c>
@@ -9708,6 +9956,10 @@
     </row>
     <row r="65" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="29"/>
+      <c r="C65" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A65,$Q$2:$Q$124,0))-$U65,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q65" s="1" t="n">
         <v>1319169</v>
       </c>
@@ -9813,6 +10065,10 @@
     </row>
     <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="28"/>
+      <c r="C66" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A66,$Q$2:$Q$124,0))-$U66,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q66" s="1" t="n">
         <v>1324508</v>
       </c>
@@ -9915,6 +10171,10 @@
     </row>
     <row r="67" customFormat="false" ht="565.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="29"/>
+      <c r="C67" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A67,$Q$2:$Q$124,0))-$U67,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q67" s="1" t="n">
         <v>1388552</v>
       </c>
@@ -10026,6 +10286,10 @@
     </row>
     <row r="68" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="28"/>
+      <c r="C68" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A68,$Q$2:$Q$124,0))-$U68,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q68" s="1" t="n">
         <v>1446350</v>
       </c>
@@ -10134,6 +10398,10 @@
     </row>
     <row r="69" customFormat="false" ht="1021.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="29"/>
+      <c r="C69" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A69,$Q$2:$Q$124,0))-$U69,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q69" s="1" t="n">
         <v>1451350</v>
       </c>
@@ -10242,6 +10510,10 @@
     </row>
     <row r="70" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="28"/>
+      <c r="C70" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A70,$Q$2:$Q$124,0))-$U70,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q70" s="1" t="n">
         <v>1474683</v>
       </c>
@@ -10347,6 +10619,10 @@
     </row>
     <row r="71" customFormat="false" ht="323.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29"/>
+      <c r="C71" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A71,$Q$2:$Q$124,0))-$U71,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q71" s="1" t="n">
         <v>1501012</v>
       </c>
@@ -10458,6 +10734,10 @@
     </row>
     <row r="72" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="28"/>
+      <c r="C72" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A72,$Q$2:$Q$124,0))-$U72,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q72" s="1" t="n">
         <v>1523115</v>
       </c>
@@ -10566,6 +10846,10 @@
     </row>
     <row r="73" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="29"/>
+      <c r="C73" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A73,$Q$2:$Q$124,0))-$U73,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q73" s="1" t="n">
         <v>1537281</v>
       </c>
@@ -10677,6 +10961,10 @@
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28"/>
+      <c r="C74" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A74,$Q$2:$Q$124,0))-$U74,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q74" s="1" t="n">
         <v>1545532</v>
       </c>
@@ -10782,6 +11070,10 @@
     </row>
     <row r="75" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="29"/>
+      <c r="C75" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A75,$Q$2:$Q$124,0))-$U75,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q75" s="1" t="n">
         <v>1567070</v>
       </c>
@@ -10893,6 +11185,10 @@
     </row>
     <row r="76" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="28"/>
+      <c r="C76" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A76,$Q$2:$Q$124,0))-$U76,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q76" s="1" t="n">
         <v>1583715</v>
       </c>
@@ -11004,6 +11300,10 @@
     </row>
     <row r="77" customFormat="false" ht="511.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="29"/>
+      <c r="C77" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A77,$Q$2:$Q$124,0))-$U77,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q77" s="1" t="n">
         <v>1584554</v>
       </c>
@@ -11112,6 +11412,10 @@
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="28"/>
+      <c r="C78" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A78,$Q$2:$Q$124,0))-$U78,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q78" s="1" t="n">
         <v>1584554</v>
       </c>
@@ -11220,6 +11524,10 @@
     </row>
     <row r="79" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="29"/>
+      <c r="C79" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A79,$Q$2:$Q$124,0))-$U79,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q79" s="1" t="n">
         <v>1590900</v>
       </c>
@@ -11328,6 +11636,10 @@
     </row>
     <row r="80" customFormat="false" ht="565.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28"/>
+      <c r="C80" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A80,$Q$2:$Q$124,0))-$U80,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q80" s="1" t="n">
         <v>1595529</v>
       </c>
@@ -11436,6 +11748,10 @@
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="29"/>
+      <c r="C81" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A81,$Q$2:$Q$124,0))-$U81,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q81" s="1" t="n">
         <v>1617422</v>
       </c>
@@ -11547,6 +11863,10 @@
     </row>
     <row r="82" customFormat="false" ht="579.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="28"/>
+      <c r="C82" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A82,$Q$2:$Q$124,0))-$U82,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q82" s="1" t="n">
         <v>1623339</v>
       </c>
@@ -11655,6 +11975,10 @@
     </row>
     <row r="83" customFormat="false" ht="283.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="29"/>
+      <c r="C83" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A83,$Q$2:$Q$124,0))-$U83,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q83" s="1" t="n">
         <v>1709591</v>
       </c>
@@ -11766,6 +12090,10 @@
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="28"/>
+      <c r="C84" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A84,$Q$2:$Q$124,0))-$U84,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q84" s="1" t="n">
         <v>1711553</v>
       </c>
@@ -11871,6 +12199,10 @@
     </row>
     <row r="85" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="29"/>
+      <c r="C85" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A85,$Q$2:$Q$124,0))-$U85,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q85" s="1" t="n">
         <v>1773563</v>
       </c>
@@ -11982,6 +12314,10 @@
     </row>
     <row r="86" customFormat="false" ht="565.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="28"/>
+      <c r="C86" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A86,$Q$2:$Q$124,0))-$U86,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q86" s="1" t="n">
         <v>1793157</v>
       </c>
@@ -12090,6 +12426,10 @@
     </row>
     <row r="87" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="29"/>
+      <c r="C87" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A87,$Q$2:$Q$124,0))-$U87,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q87" s="1" t="n">
         <v>1812288</v>
       </c>
@@ -12198,6 +12538,10 @@
     </row>
     <row r="88" customFormat="false" ht="833.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="28"/>
+      <c r="C88" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A88,$Q$2:$Q$124,0))-$U88,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q88" s="1" t="n">
         <v>1837954</v>
       </c>
@@ -12309,6 +12653,10 @@
     </row>
     <row r="89" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="29"/>
+      <c r="C89" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A89,$Q$2:$Q$124,0))-$U89,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q89" s="1" t="n">
         <v>1898089</v>
       </c>
@@ -12417,6 +12765,10 @@
     </row>
     <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="28"/>
+      <c r="C90" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A90,$Q$2:$Q$124,0))-$U90,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q90" s="1" t="n">
         <v>1901428</v>
       </c>
@@ -12528,6 +12880,10 @@
     </row>
     <row r="91" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="29"/>
+      <c r="C91" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A91,$Q$2:$Q$124,0))-$U91,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q91" s="1" t="n">
         <v>1927946</v>
       </c>
@@ -12636,6 +12992,10 @@
     </row>
     <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="28"/>
+      <c r="C92" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A92,$Q$2:$Q$124,0))-$U92,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q92" s="1" t="n">
         <v>1937275</v>
       </c>
@@ -12744,6 +13104,10 @@
     </row>
     <row r="93" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="29"/>
+      <c r="C93" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A93,$Q$2:$Q$124,0))-$U93,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q93" s="1" t="n">
         <v>1979384</v>
       </c>
@@ -12852,6 +13216,10 @@
     </row>
     <row r="94" customFormat="false" ht="766.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="28"/>
+      <c r="C94" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A94,$Q$2:$Q$124,0))-$U94,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q94" s="1" t="n">
         <v>2008686</v>
       </c>
@@ -12960,6 +13328,10 @@
     </row>
     <row r="95" customFormat="false" ht="1129.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="29"/>
+      <c r="C95" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A95,$Q$2:$Q$124,0))-$U95,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q95" s="1" t="n">
         <v>2011391</v>
       </c>
@@ -13071,6 +13443,10 @@
     </row>
     <row r="96" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="28"/>
+      <c r="C96" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A96,$Q$2:$Q$124,0))-$U96,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q96" s="1" t="n">
         <v>2011391</v>
       </c>
@@ -13179,6 +13555,10 @@
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="29"/>
+      <c r="C97" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A97,$Q$2:$Q$124,0))-$U97,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q97" s="1" t="n">
         <v>2031862</v>
       </c>
@@ -13290,6 +13670,10 @@
     </row>
     <row r="98" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="28"/>
+      <c r="C98" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A98,$Q$2:$Q$124,0))-$U98,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q98" s="1" t="n">
         <v>2037743</v>
       </c>
@@ -13401,6 +13785,10 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="29"/>
+      <c r="C99" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A99,$Q$2:$Q$124,0))-$U99,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q99" s="1" t="n">
         <v>2039733</v>
       </c>
@@ -13512,6 +13900,10 @@
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="28"/>
+      <c r="C100" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A100,$Q$2:$Q$124,0))-$U100,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q100" s="1" t="n">
         <v>2065829</v>
       </c>
@@ -13620,6 +14012,10 @@
     </row>
     <row r="101" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="29"/>
+      <c r="C101" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A101,$Q$2:$Q$124,0))-$U101,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q101" s="1" t="n">
         <v>2093241</v>
       </c>
@@ -13728,6 +14124,10 @@
     </row>
     <row r="102" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="28"/>
+      <c r="C102" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A102,$Q$2:$Q$124,0))-$U102,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q102" s="1" t="n">
         <v>2095972</v>
       </c>
@@ -13836,6 +14236,10 @@
     </row>
     <row r="103" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="29"/>
+      <c r="C103" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A103,$Q$2:$Q$124,0))-$U103,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q103" s="1" t="n">
         <v>2146934</v>
       </c>
@@ -13944,6 +14348,10 @@
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="28"/>
+      <c r="C104" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A104,$Q$2:$Q$124,0))-$U104,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q104" s="1" t="n">
         <v>2147260</v>
       </c>
@@ -14055,6 +14463,10 @@
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="29"/>
+      <c r="C105" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A105,$Q$2:$Q$124,0))-$U105,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q105" s="1" t="n">
         <v>2201853</v>
       </c>
@@ -14160,6 +14572,10 @@
     </row>
     <row r="106" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="28"/>
+      <c r="C106" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A106,$Q$2:$Q$124,0))-$U106,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q106" s="1" t="n">
         <v>2201853</v>
       </c>
@@ -14268,6 +14684,10 @@
     </row>
     <row r="107" customFormat="false" ht="229.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="29"/>
+      <c r="C107" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A107,$Q$2:$Q$124,0))-$U107,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q107" s="1" t="n">
         <v>2230181</v>
       </c>
@@ -14376,6 +14796,10 @@
     </row>
     <row r="108" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="28"/>
+      <c r="C108" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A108,$Q$2:$Q$124,0))-$U108,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q108" s="1" t="n">
         <v>2230181</v>
       </c>
@@ -14484,6 +14908,10 @@
     </row>
     <row r="109" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="29"/>
+      <c r="C109" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A109,$Q$2:$Q$124,0))-$U109,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q109" s="1" t="n">
         <v>2254084</v>
       </c>
@@ -14589,6 +15017,10 @@
     </row>
     <row r="110" customFormat="false" ht="350.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="28"/>
+      <c r="C110" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A110,$Q$2:$Q$124,0))-$U110,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q110" s="1" t="n">
         <v>2264703</v>
       </c>
@@ -14700,6 +15132,10 @@
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="29"/>
+      <c r="C111" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A111,$Q$2:$Q$124,0))-$U111,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q111" s="1" t="n">
         <v>2274015</v>
       </c>
@@ -14808,6 +15244,10 @@
     </row>
     <row r="112" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="28"/>
+      <c r="C112" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A112,$Q$2:$Q$124,0))-$U112,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q112" s="1" t="n">
         <v>2276762</v>
       </c>
@@ -14916,6 +15356,10 @@
     </row>
     <row r="113" customFormat="false" ht="229.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="29"/>
+      <c r="C113" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A113,$Q$2:$Q$124,0))-$U113,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q113" s="1" t="n">
         <v>2283745</v>
       </c>
@@ -15030,6 +15474,10 @@
     </row>
     <row r="114" customFormat="false" ht="1397.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="28"/>
+      <c r="C114" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A114,$Q$2:$Q$124,0))-$U114,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q114" s="1" t="n">
         <v>2288108</v>
       </c>
@@ -15138,6 +15586,10 @@
     </row>
     <row r="115" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="29"/>
+      <c r="C115" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A115,$Q$2:$Q$124,0))-$U115,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q115" s="1" t="n">
         <v>2306015</v>
       </c>
@@ -15246,6 +15698,10 @@
     </row>
     <row r="116" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="28"/>
+      <c r="C116" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A116,$Q$2:$Q$124,0))-$U116,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q116" s="1" t="n">
         <v>2309938</v>
       </c>
@@ -15354,6 +15810,10 @@
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="29"/>
+      <c r="C117" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A117,$Q$2:$Q$124,0))-$U117,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q117" s="1" t="n">
         <v>2362713</v>
       </c>
@@ -15456,6 +15916,10 @@
     </row>
     <row r="118" customFormat="false" ht="873.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="28"/>
+      <c r="C118" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A118,$Q$2:$Q$124,0))-$U118,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q118" s="1" t="n">
         <v>2431872</v>
       </c>
@@ -15570,6 +16034,10 @@
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="29"/>
+      <c r="C119" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A119,$Q$2:$Q$124,0))-$U119,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q119" s="1" t="n">
         <v>2435543</v>
       </c>
@@ -15681,6 +16149,10 @@
     </row>
     <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="28"/>
+      <c r="C120" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A120,$Q$2:$Q$124,0))-$U120,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q120" s="1" t="n">
         <v>2464758</v>
       </c>
@@ -15789,6 +16261,10 @@
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="29"/>
+      <c r="C121" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A121,$Q$2:$Q$124,0))-$U121,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q121" s="1" t="n">
         <v>2476560</v>
       </c>
@@ -15897,6 +16373,10 @@
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="28"/>
+      <c r="C122" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A122,$Q$2:$Q$124,0))-$U122,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q122" s="1" t="n">
         <v>2494920</v>
       </c>
@@ -16002,6 +16482,10 @@
     </row>
     <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="29"/>
+      <c r="C123" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A123,$Q$2:$Q$124,0))-$U123,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q123" s="1" t="n">
         <v>2556130</v>
       </c>
@@ -16110,6 +16594,10 @@
     </row>
     <row r="124" customFormat="false" ht="229.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="28"/>
+      <c r="C124" s="1" t="n">
+        <f aca="false">IFERROR(INDEX($Y$2:$Y$124,MATCH($A124,$Q$2:$Q$124,0))-$U124,0)</f>
+        <v>0</v>
+      </c>
       <c r="Q124" s="1" t="n">
         <v>2590378</v>
       </c>
